--- a/Hasan Panwar/new students data.xlsx
+++ b/Hasan Panwar/new students data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZEESHAN COMPUTERS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Hasan Panwar\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDDA012-120E-4892-ADD5-9CE3EA5A6748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE" sheetId="1" r:id="rId1"/>
@@ -2321,6 +2322,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">              KHALID AHMED                </t>
@@ -3434,7 +3436,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
@@ -3554,6 +3556,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3562,6 +3565,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3740,7 +3744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3804,9 +3808,6 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3821,12 +3822,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3836,12 +3831,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -3868,12 +3857,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3942,7 +3925,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3953,15 +3936,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3973,6 +3947,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4008,7 +3991,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4044,7 +4033,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4085,7 +4080,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4121,7 +4122,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4162,7 +4169,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4198,7 +4211,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4239,7 +4258,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4275,7 +4300,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4561,7 +4592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4584,230 +4615,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="50" t="s">
         <v>602</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
-      <c r="N8" s="57"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="59" t="s">
+      <c r="G11" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="I11" s="59" t="s">
+      <c r="I11" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="J11" s="59" t="s">
+      <c r="J11" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="60" t="s">
+      <c r="K11" s="35"/>
+      <c r="L11" s="53" t="s">
         <v>878</v>
       </c>
-      <c r="M11" s="59" t="s">
+      <c r="M11" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="59" t="s">
+      <c r="N11" s="52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="41" t="s">
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="36" t="s">
         <v>753</v>
       </c>
-      <c r="L12" s="61"/>
-      <c r="M12" s="59"/>
-      <c r="N12" s="59"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -6968,7 +6999,7 @@
       <c r="J64" s="23">
         <v>43264</v>
       </c>
-      <c r="K64" s="42" t="s">
+      <c r="K64" s="37" t="s">
         <v>985</v>
       </c>
       <c r="L64" s="23"/>
@@ -7010,7 +7041,7 @@
       <c r="J65" s="23">
         <v>43265</v>
       </c>
-      <c r="K65" s="42" t="s">
+      <c r="K65" s="37" t="s">
         <v>985</v>
       </c>
       <c r="L65" s="23"/>
@@ -7052,7 +7083,7 @@
       <c r="J66" s="23">
         <v>43266</v>
       </c>
-      <c r="K66" s="42" t="s">
+      <c r="K66" s="37" t="s">
         <v>985</v>
       </c>
       <c r="L66" s="23"/>
@@ -7094,7 +7125,7 @@
       <c r="J67" s="23">
         <v>43267</v>
       </c>
-      <c r="K67" s="42" t="s">
+      <c r="K67" s="37" t="s">
         <v>872</v>
       </c>
       <c r="L67" s="23"/>
@@ -7136,7 +7167,7 @@
       <c r="J68" s="23">
         <v>43268</v>
       </c>
-      <c r="K68" s="42" t="s">
+      <c r="K68" s="37" t="s">
         <v>1095</v>
       </c>
       <c r="L68" s="24" t="s">
@@ -7180,7 +7211,7 @@
       <c r="J69" s="23">
         <v>43269</v>
       </c>
-      <c r="K69" s="42" t="s">
+      <c r="K69" s="37" t="s">
         <v>984</v>
       </c>
       <c r="L69" s="24" t="s">
@@ -7224,7 +7255,7 @@
       <c r="J70" s="23">
         <v>43270</v>
       </c>
-      <c r="K70" s="42" t="s">
+      <c r="K70" s="37" t="s">
         <v>984</v>
       </c>
       <c r="L70" s="24"/>
@@ -7266,7 +7297,7 @@
       <c r="J71" s="23">
         <v>43271</v>
       </c>
-      <c r="K71" s="42" t="s">
+      <c r="K71" s="37" t="s">
         <v>720</v>
       </c>
       <c r="L71" s="24"/>
@@ -7308,7 +7339,7 @@
       <c r="J72" s="23">
         <v>43272</v>
       </c>
-      <c r="K72" s="42" t="s">
+      <c r="K72" s="37" t="s">
         <v>1096</v>
       </c>
       <c r="L72" s="24" t="s">
@@ -7352,7 +7383,7 @@
       <c r="J73" s="23">
         <v>43273</v>
       </c>
-      <c r="K73" s="42" t="s">
+      <c r="K73" s="37" t="s">
         <v>1096</v>
       </c>
       <c r="L73" s="24" t="s">
@@ -7396,7 +7427,7 @@
       <c r="J74" s="23">
         <v>43274</v>
       </c>
-      <c r="K74" s="42"/>
+      <c r="K74" s="37"/>
       <c r="L74" s="24"/>
       <c r="M74" s="17">
         <v>45148</v>
@@ -7436,7 +7467,7 @@
       <c r="J75" s="23">
         <v>43275</v>
       </c>
-      <c r="K75" s="42" t="s">
+      <c r="K75" s="37" t="s">
         <v>1097</v>
       </c>
       <c r="L75" s="24"/>
@@ -7478,7 +7509,7 @@
       <c r="J76" s="23">
         <v>43276</v>
       </c>
-      <c r="K76" s="42"/>
+      <c r="K76" s="37"/>
       <c r="L76" s="24"/>
       <c r="M76" s="17">
         <v>45148</v>
@@ -7518,7 +7549,7 @@
       <c r="J77" s="23">
         <v>43277</v>
       </c>
-      <c r="K77" s="42" t="s">
+      <c r="K77" s="37" t="s">
         <v>1098</v>
       </c>
       <c r="L77" s="24" t="s">
@@ -7562,7 +7593,7 @@
       <c r="J78" s="23">
         <v>43278</v>
       </c>
-      <c r="K78" s="42" t="s">
+      <c r="K78" s="37" t="s">
         <v>1047</v>
       </c>
       <c r="L78" s="24"/>
@@ -7604,7 +7635,7 @@
       <c r="J79" s="23">
         <v>43279</v>
       </c>
-      <c r="K79" s="42" t="s">
+      <c r="K79" s="37" t="s">
         <v>983</v>
       </c>
       <c r="L79" s="24"/>
@@ -7646,7 +7677,7 @@
       <c r="J80" s="23">
         <v>43280</v>
       </c>
-      <c r="K80" s="42" t="s">
+      <c r="K80" s="37" t="s">
         <v>1099</v>
       </c>
       <c r="L80" s="24" t="s">
@@ -7690,7 +7721,7 @@
       <c r="J81" s="23">
         <v>43281</v>
       </c>
-      <c r="K81" s="42" t="s">
+      <c r="K81" s="37" t="s">
         <v>872</v>
       </c>
       <c r="L81" s="24"/>
@@ -7732,7 +7763,7 @@
       <c r="J82" s="23">
         <v>43282</v>
       </c>
-      <c r="K82" s="42"/>
+      <c r="K82" s="37"/>
       <c r="L82" s="24"/>
       <c r="M82" s="17">
         <v>45148</v>
@@ -7772,7 +7803,7 @@
       <c r="J83" s="23">
         <v>43283</v>
       </c>
-      <c r="K83" s="42"/>
+      <c r="K83" s="37"/>
       <c r="L83" s="24" t="s">
         <v>883</v>
       </c>
@@ -7814,7 +7845,7 @@
       <c r="J84" s="23">
         <v>43284</v>
       </c>
-      <c r="K84" s="42" t="s">
+      <c r="K84" s="37" t="s">
         <v>982</v>
       </c>
       <c r="L84" s="24"/>
@@ -7856,7 +7887,7 @@
       <c r="J85" s="23">
         <v>43285</v>
       </c>
-      <c r="K85" s="42" t="s">
+      <c r="K85" s="37" t="s">
         <v>982</v>
       </c>
       <c r="L85" s="24"/>
@@ -7898,7 +7929,7 @@
       <c r="J86" s="23">
         <v>43286</v>
       </c>
-      <c r="K86" s="42" t="s">
+      <c r="K86" s="37" t="s">
         <v>982</v>
       </c>
       <c r="L86" s="24" t="s">
@@ -7942,7 +7973,7 @@
       <c r="J87" s="23">
         <v>43287</v>
       </c>
-      <c r="K87" s="42" t="s">
+      <c r="K87" s="37" t="s">
         <v>1100</v>
       </c>
       <c r="L87" s="24" t="s">
@@ -7986,7 +8017,7 @@
       <c r="J88" s="23">
         <v>43288</v>
       </c>
-      <c r="K88" s="42" t="s">
+      <c r="K88" s="37" t="s">
         <v>960</v>
       </c>
       <c r="L88" s="24"/>
@@ -8028,7 +8059,7 @@
       <c r="J89" s="23">
         <v>43289</v>
       </c>
-      <c r="K89" s="42" t="s">
+      <c r="K89" s="37" t="s">
         <v>692</v>
       </c>
       <c r="L89" s="24"/>
@@ -8070,7 +8101,7 @@
       <c r="J90" s="23">
         <v>43290</v>
       </c>
-      <c r="K90" s="42" t="s">
+      <c r="K90" s="37" t="s">
         <v>692</v>
       </c>
       <c r="L90" s="24"/>
@@ -8112,7 +8143,7 @@
       <c r="J91" s="23">
         <v>43291</v>
       </c>
-      <c r="K91" s="42" t="s">
+      <c r="K91" s="37" t="s">
         <v>869</v>
       </c>
       <c r="L91" s="24" t="s">
@@ -8156,7 +8187,7 @@
       <c r="J92" s="23">
         <v>43292</v>
       </c>
-      <c r="K92" s="42" t="s">
+      <c r="K92" s="37" t="s">
         <v>869</v>
       </c>
       <c r="L92" s="24" t="s">
@@ -8200,7 +8231,7 @@
       <c r="J93" s="23">
         <v>43293</v>
       </c>
-      <c r="K93" s="42" t="s">
+      <c r="K93" s="37" t="s">
         <v>981</v>
       </c>
       <c r="L93" s="24" t="s">
@@ -8244,7 +8275,7 @@
       <c r="J94" s="23">
         <v>43294</v>
       </c>
-      <c r="K94" s="42" t="s">
+      <c r="K94" s="37" t="s">
         <v>980</v>
       </c>
       <c r="L94" s="24" t="s">
@@ -8288,7 +8319,7 @@
       <c r="J95" s="23">
         <v>43295</v>
       </c>
-      <c r="K95" s="42" t="s">
+      <c r="K95" s="37" t="s">
         <v>979</v>
       </c>
       <c r="L95" s="24"/>
@@ -8330,7 +8361,7 @@
       <c r="J96" s="23">
         <v>43296</v>
       </c>
-      <c r="K96" s="42" t="s">
+      <c r="K96" s="37" t="s">
         <v>978</v>
       </c>
       <c r="L96" s="24" t="s">
@@ -8374,7 +8405,7 @@
       <c r="J97" s="23">
         <v>43297</v>
       </c>
-      <c r="K97" s="42" t="s">
+      <c r="K97" s="37" t="s">
         <v>1101</v>
       </c>
       <c r="L97" s="24" t="s">
@@ -8418,7 +8449,7 @@
       <c r="J98" s="23">
         <v>43298</v>
       </c>
-      <c r="K98" s="42" t="s">
+      <c r="K98" s="37" t="s">
         <v>977</v>
       </c>
       <c r="L98" s="24" t="s">
@@ -8462,7 +8493,7 @@
       <c r="J99" s="23">
         <v>43299</v>
       </c>
-      <c r="K99" s="42" t="s">
+      <c r="K99" s="37" t="s">
         <v>977</v>
       </c>
       <c r="L99" s="24"/>
@@ -8504,7 +8535,7 @@
       <c r="J100" s="23">
         <v>43300</v>
       </c>
-      <c r="K100" s="42" t="s">
+      <c r="K100" s="37" t="s">
         <v>1082</v>
       </c>
       <c r="L100" s="24"/>
@@ -8546,7 +8577,7 @@
       <c r="J101" s="23">
         <v>43301</v>
       </c>
-      <c r="K101" s="42" t="s">
+      <c r="K101" s="37" t="s">
         <v>976</v>
       </c>
       <c r="L101" s="24" t="s">
@@ -8590,7 +8621,7 @@
       <c r="J102" s="23">
         <v>43302</v>
       </c>
-      <c r="K102" s="42" t="s">
+      <c r="K102" s="37" t="s">
         <v>975</v>
       </c>
       <c r="L102" s="24" t="s">
@@ -8634,7 +8665,7 @@
       <c r="J103" s="23">
         <v>43303</v>
       </c>
-      <c r="K103" s="42"/>
+      <c r="K103" s="37"/>
       <c r="L103" s="24" t="s">
         <v>883</v>
       </c>
@@ -8676,7 +8707,7 @@
       <c r="J104" s="23">
         <v>43304</v>
       </c>
-      <c r="K104" s="44" t="s">
+      <c r="K104" s="39" t="s">
         <v>915</v>
       </c>
       <c r="L104" s="24" t="s">
@@ -8720,7 +8751,7 @@
       <c r="J105" s="23">
         <v>43305</v>
       </c>
-      <c r="K105" s="44" t="s">
+      <c r="K105" s="39" t="s">
         <v>915</v>
       </c>
       <c r="L105" s="24" t="s">
@@ -8764,7 +8795,7 @@
       <c r="J106" s="23">
         <v>43306</v>
       </c>
-      <c r="K106" s="44" t="s">
+      <c r="K106" s="39" t="s">
         <v>916</v>
       </c>
       <c r="L106" s="24"/>
@@ -8806,7 +8837,7 @@
       <c r="J107" s="23">
         <v>43307</v>
       </c>
-      <c r="K107" s="42" t="s">
+      <c r="K107" s="37" t="s">
         <v>1102</v>
       </c>
       <c r="L107" s="24"/>
@@ -8848,7 +8879,7 @@
       <c r="J108" s="23">
         <v>43308</v>
       </c>
-      <c r="K108" s="44" t="s">
+      <c r="K108" s="39" t="s">
         <v>917</v>
       </c>
       <c r="L108" s="24" t="s">
@@ -8892,7 +8923,7 @@
       <c r="J109" s="23">
         <v>43309</v>
       </c>
-      <c r="K109" s="44" t="s">
+      <c r="K109" s="39" t="s">
         <v>917</v>
       </c>
       <c r="L109" s="24" t="s">
@@ -8936,7 +8967,7 @@
       <c r="J110" s="23">
         <v>43310</v>
       </c>
-      <c r="K110" s="44" t="s">
+      <c r="K110" s="39" t="s">
         <v>914</v>
       </c>
       <c r="L110" s="24" t="s">
@@ -8980,7 +9011,7 @@
       <c r="J111" s="23">
         <v>43311</v>
       </c>
-      <c r="K111" s="44" t="s">
+      <c r="K111" s="39" t="s">
         <v>918</v>
       </c>
       <c r="L111" s="24"/>
@@ -9022,7 +9053,7 @@
       <c r="J112" s="23">
         <v>43312</v>
       </c>
-      <c r="K112" s="44" t="s">
+      <c r="K112" s="39" t="s">
         <v>919</v>
       </c>
       <c r="L112" s="24"/>
@@ -9064,7 +9095,7 @@
       <c r="J113" s="23">
         <v>43313</v>
       </c>
-      <c r="K113" s="42" t="s">
+      <c r="K113" s="37" t="s">
         <v>974</v>
       </c>
       <c r="L113" s="24" t="s">
@@ -9106,7 +9137,7 @@
       <c r="J114" s="23">
         <v>43314</v>
       </c>
-      <c r="K114" s="42" t="s">
+      <c r="K114" s="37" t="s">
         <v>972</v>
       </c>
       <c r="L114" s="24"/>
@@ -9148,7 +9179,7 @@
       <c r="J115" s="23">
         <v>43315</v>
       </c>
-      <c r="K115" s="42"/>
+      <c r="K115" s="37"/>
       <c r="L115" s="24"/>
       <c r="M115" s="17">
         <v>45148</v>
@@ -9188,7 +9219,7 @@
       <c r="J116" s="23">
         <v>43316</v>
       </c>
-      <c r="K116" s="42" t="s">
+      <c r="K116" s="37" t="s">
         <v>965</v>
       </c>
       <c r="L116" s="24"/>
@@ -9230,7 +9261,7 @@
       <c r="J117" s="23">
         <v>43317</v>
       </c>
-      <c r="K117" s="42" t="s">
+      <c r="K117" s="37" t="s">
         <v>920</v>
       </c>
       <c r="L117" s="24" t="s">
@@ -9274,7 +9305,7 @@
       <c r="J118" s="23">
         <v>43318</v>
       </c>
-      <c r="K118" s="42" t="s">
+      <c r="K118" s="37" t="s">
         <v>920</v>
       </c>
       <c r="L118" s="24" t="s">
@@ -9362,7 +9393,7 @@
       <c r="J120" s="23">
         <v>43320</v>
       </c>
-      <c r="K120" s="42" t="s">
+      <c r="K120" s="37" t="s">
         <v>1111</v>
       </c>
       <c r="L120" s="24"/>
@@ -9404,7 +9435,7 @@
       <c r="J121" s="23">
         <v>43321</v>
       </c>
-      <c r="K121" s="42" t="s">
+      <c r="K121" s="37" t="s">
         <v>921</v>
       </c>
       <c r="L121" s="24"/>
@@ -9446,7 +9477,7 @@
       <c r="J122" s="23">
         <v>43322</v>
       </c>
-      <c r="K122" s="42" t="s">
+      <c r="K122" s="37" t="s">
         <v>1103</v>
       </c>
       <c r="L122" s="24" t="s">
@@ -9490,7 +9521,7 @@
       <c r="J123" s="23">
         <v>43323</v>
       </c>
-      <c r="K123" s="42" t="s">
+      <c r="K123" s="37" t="s">
         <v>940</v>
       </c>
       <c r="L123" s="24" t="s">
@@ -9534,7 +9565,7 @@
       <c r="J124" s="23">
         <v>43324</v>
       </c>
-      <c r="K124" s="45" t="s">
+      <c r="K124" s="40" t="s">
         <v>920</v>
       </c>
       <c r="L124" s="24"/>
@@ -9576,7 +9607,7 @@
       <c r="J125" s="23">
         <v>43325</v>
       </c>
-      <c r="K125" s="45" t="s">
+      <c r="K125" s="40" t="s">
         <v>971</v>
       </c>
       <c r="L125" s="4"/>
@@ -9618,7 +9649,7 @@
       <c r="J126" s="23">
         <v>43326</v>
       </c>
-      <c r="K126" s="42" t="s">
+      <c r="K126" s="37" t="s">
         <v>970</v>
       </c>
       <c r="L126" s="24"/>
@@ -9660,7 +9691,7 @@
       <c r="J127" s="23">
         <v>43327</v>
       </c>
-      <c r="K127" s="44" t="s">
+      <c r="K127" s="39" t="s">
         <v>921</v>
       </c>
       <c r="L127" s="24"/>
@@ -9702,7 +9733,7 @@
       <c r="J128" s="23">
         <v>43328</v>
       </c>
-      <c r="K128" s="42" t="s">
+      <c r="K128" s="37" t="s">
         <v>923</v>
       </c>
       <c r="L128" s="24"/>
@@ -9744,7 +9775,7 @@
       <c r="J129" s="23">
         <v>43329</v>
       </c>
-      <c r="K129" s="42" t="s">
+      <c r="K129" s="37" t="s">
         <v>923</v>
       </c>
       <c r="L129" s="24"/>
@@ -9786,7 +9817,7 @@
       <c r="J130" s="23">
         <v>43330</v>
       </c>
-      <c r="K130" s="42" t="s">
+      <c r="K130" s="37" t="s">
         <v>923</v>
       </c>
       <c r="L130" s="24"/>
@@ -9828,7 +9859,7 @@
       <c r="J131" s="23">
         <v>43331</v>
       </c>
-      <c r="K131" s="42" t="s">
+      <c r="K131" s="37" t="s">
         <v>1104</v>
       </c>
       <c r="L131" s="24"/>
@@ -9870,7 +9901,7 @@
       <c r="J132" s="23">
         <v>43332</v>
       </c>
-      <c r="K132" s="44" t="s">
+      <c r="K132" s="39" t="s">
         <v>922</v>
       </c>
       <c r="L132" s="24"/>
@@ -9912,7 +9943,7 @@
       <c r="J133" s="23">
         <v>43333</v>
       </c>
-      <c r="K133" s="42" t="s">
+      <c r="K133" s="37" t="s">
         <v>969</v>
       </c>
       <c r="L133" s="24"/>
@@ -9954,7 +9985,7 @@
       <c r="J134" s="23">
         <v>43334</v>
       </c>
-      <c r="K134" s="42" t="s">
+      <c r="K134" s="37" t="s">
         <v>968</v>
       </c>
       <c r="L134" s="24"/>
@@ -9996,7 +10027,7 @@
       <c r="J135" s="23">
         <v>43335</v>
       </c>
-      <c r="K135" s="44" t="s">
+      <c r="K135" s="39" t="s">
         <v>923</v>
       </c>
       <c r="L135" s="24"/>
@@ -10038,7 +10069,7 @@
       <c r="J136" s="23">
         <v>43336</v>
       </c>
-      <c r="K136" s="44" t="s">
+      <c r="K136" s="39" t="s">
         <v>923</v>
       </c>
       <c r="L136" s="24"/>
@@ -10080,7 +10111,7 @@
       <c r="J137" s="23">
         <v>43337</v>
       </c>
-      <c r="K137" s="44" t="s">
+      <c r="K137" s="39" t="s">
         <v>923</v>
       </c>
       <c r="L137" s="24"/>
@@ -10122,7 +10153,7 @@
       <c r="J138" s="23">
         <v>43338</v>
       </c>
-      <c r="K138" s="42" t="s">
+      <c r="K138" s="37" t="s">
         <v>967</v>
       </c>
       <c r="L138" s="24"/>
@@ -10164,7 +10195,7 @@
       <c r="J139" s="23">
         <v>43339</v>
       </c>
-      <c r="K139" s="42" t="s">
+      <c r="K139" s="37" t="s">
         <v>698</v>
       </c>
       <c r="L139" s="24"/>
@@ -10206,7 +10237,7 @@
       <c r="J140" s="23">
         <v>43340</v>
       </c>
-      <c r="K140" s="44" t="s">
+      <c r="K140" s="39" t="s">
         <v>924</v>
       </c>
       <c r="L140" s="24"/>
@@ -10248,7 +10279,7 @@
       <c r="J141" s="23">
         <v>43341</v>
       </c>
-      <c r="K141" s="44" t="s">
+      <c r="K141" s="39" t="s">
         <v>924</v>
       </c>
       <c r="L141" s="24"/>
@@ -10290,7 +10321,7 @@
       <c r="J142" s="23">
         <v>43342</v>
       </c>
-      <c r="K142" s="44" t="s">
+      <c r="K142" s="39" t="s">
         <v>924</v>
       </c>
       <c r="L142" s="24"/>
@@ -10332,7 +10363,7 @@
       <c r="J143" s="23">
         <v>43343</v>
       </c>
-      <c r="K143" s="44" t="s">
+      <c r="K143" s="39" t="s">
         <v>925</v>
       </c>
       <c r="L143" s="24" t="s">
@@ -10376,7 +10407,7 @@
       <c r="J144" s="23">
         <v>43344</v>
       </c>
-      <c r="K144" s="44" t="s">
+      <c r="K144" s="39" t="s">
         <v>925</v>
       </c>
       <c r="L144" s="24" t="s">
@@ -10420,7 +10451,7 @@
       <c r="J145" s="23">
         <v>43345</v>
       </c>
-      <c r="K145" s="44" t="s">
+      <c r="K145" s="39" t="s">
         <v>926</v>
       </c>
       <c r="L145" s="24" t="s">
@@ -10464,7 +10495,7 @@
       <c r="J146" s="23">
         <v>43346</v>
       </c>
-      <c r="K146" s="44" t="s">
+      <c r="K146" s="39" t="s">
         <v>927</v>
       </c>
       <c r="L146" s="24" t="s">
@@ -10508,7 +10539,7 @@
       <c r="J147" s="23">
         <v>43347</v>
       </c>
-      <c r="K147" s="44" t="s">
+      <c r="K147" s="39" t="s">
         <v>928</v>
       </c>
       <c r="L147" s="24" t="s">
@@ -10552,7 +10583,7 @@
       <c r="J148" s="23">
         <v>43348</v>
       </c>
-      <c r="K148" s="44" t="s">
+      <c r="K148" s="39" t="s">
         <v>929</v>
       </c>
       <c r="L148" s="24" t="s">
@@ -10596,7 +10627,7 @@
       <c r="J149" s="23">
         <v>43349</v>
       </c>
-      <c r="K149" s="44" t="s">
+      <c r="K149" s="39" t="s">
         <v>930</v>
       </c>
       <c r="L149" s="24" t="s">
@@ -10640,7 +10671,7 @@
       <c r="J150" s="23">
         <v>43350</v>
       </c>
-      <c r="K150" s="42" t="s">
+      <c r="K150" s="37" t="s">
         <v>966</v>
       </c>
       <c r="L150" s="24" t="s">
@@ -10684,7 +10715,7 @@
       <c r="J151" s="23">
         <v>43351</v>
       </c>
-      <c r="K151" s="42" t="s">
+      <c r="K151" s="37" t="s">
         <v>965</v>
       </c>
       <c r="L151" s="24" t="s">
@@ -10921,7 +10952,7 @@
       <c r="A157" s="2">
         <v>148</v>
       </c>
-      <c r="B157" s="46">
+      <c r="B157" s="41">
         <v>1749</v>
       </c>
       <c r="C157" s="15" t="s">
@@ -10963,13 +10994,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
-      <c r="B158" s="28">
+      <c r="B158" s="27">
         <v>1750</v>
       </c>
-      <c r="C158" s="47" t="s">
+      <c r="C158" s="42" t="s">
         <v>510</v>
       </c>
-      <c r="D158" s="47" t="s">
+      <c r="D158" s="42" t="s">
         <v>955</v>
       </c>
       <c r="I158" s="1" t="s">
@@ -11042,7 +11073,7 @@
       <c r="N160" s="15"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B161" s="48">
+      <c r="B161" s="43">
         <v>1753</v>
       </c>
       <c r="C161" s="15" t="s">
@@ -11069,7 +11100,7 @@
       <c r="J161" s="23">
         <v>43361</v>
       </c>
-      <c r="K161" s="43" t="s">
+      <c r="K161" s="38" t="s">
         <v>1106</v>
       </c>
       <c r="L161" s="4" t="s">
@@ -11083,38 +11114,38 @@
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" s="51" t="s">
+      <c r="A162" s="44" t="s">
         <v>607</v>
       </c>
-      <c r="B162" s="52"/>
-      <c r="C162" s="52"/>
-      <c r="D162" s="52"/>
-      <c r="E162" s="52"/>
-      <c r="F162" s="52"/>
-      <c r="G162" s="52"/>
-      <c r="H162" s="52"/>
-      <c r="I162" s="52"/>
-      <c r="J162" s="52"/>
-      <c r="K162" s="52"/>
-      <c r="L162" s="52"/>
-      <c r="M162" s="52"/>
-      <c r="N162" s="53"/>
+      <c r="B162" s="45"/>
+      <c r="C162" s="45"/>
+      <c r="D162" s="45"/>
+      <c r="E162" s="45"/>
+      <c r="F162" s="45"/>
+      <c r="G162" s="45"/>
+      <c r="H162" s="45"/>
+      <c r="I162" s="45"/>
+      <c r="J162" s="45"/>
+      <c r="K162" s="45"/>
+      <c r="L162" s="45"/>
+      <c r="M162" s="45"/>
+      <c r="N162" s="46"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" s="54"/>
-      <c r="B163" s="55"/>
-      <c r="C163" s="55"/>
-      <c r="D163" s="55"/>
-      <c r="E163" s="55"/>
-      <c r="F163" s="55"/>
-      <c r="G163" s="55"/>
-      <c r="H163" s="55"/>
-      <c r="I163" s="55"/>
-      <c r="J163" s="55"/>
-      <c r="K163" s="55"/>
-      <c r="L163" s="55"/>
-      <c r="M163" s="55"/>
-      <c r="N163" s="56"/>
+      <c r="A163" s="47"/>
+      <c r="B163" s="48"/>
+      <c r="C163" s="48"/>
+      <c r="D163" s="48"/>
+      <c r="E163" s="48"/>
+      <c r="F163" s="48"/>
+      <c r="G163" s="48"/>
+      <c r="H163" s="48"/>
+      <c r="I163" s="48"/>
+      <c r="J163" s="48"/>
+      <c r="K163" s="48"/>
+      <c r="L163" s="48"/>
+      <c r="M163" s="48"/>
+      <c r="N163" s="49"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N164" s="3"/>
@@ -11394,7 +11425,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11420,232 +11451,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="61" t="s">
         <v>603</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="68"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="68"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="68"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="68"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="61"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="E10" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="70" t="s">
+      <c r="H10" s="63" t="s">
         <v>313</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="53" t="s">
         <v>691</v>
       </c>
-      <c r="K10" s="60" t="s">
+      <c r="K10" s="53" t="s">
         <v>878</v>
       </c>
-      <c r="L10" s="69" t="s">
+      <c r="L10" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="69" t="s">
+      <c r="N10" s="62" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="25" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="69"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="62"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
@@ -11675,19 +11706,19 @@
       <c r="I12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="38" t="s">
+      <c r="J12" s="10" t="s">
         <v>995</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="28">
         <v>41897</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="29">
         <v>45142</v>
       </c>
-      <c r="N12" s="31" t="s">
+      <c r="N12" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11719,19 +11750,19 @@
       <c r="I13" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="J13" s="38" t="s">
+      <c r="J13" s="10" t="s">
         <v>962</v>
       </c>
-      <c r="K13" s="38" t="s">
+      <c r="K13" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="28">
         <v>41487</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="29">
         <v>45142</v>
       </c>
-      <c r="N13" s="31" t="s">
+      <c r="N13" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11763,19 +11794,19 @@
       <c r="I14" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="J14" s="38" t="s">
+      <c r="J14" s="10" t="s">
         <v>1033</v>
       </c>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="28">
         <v>41715</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="29">
         <v>45142</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11807,19 +11838,19 @@
       <c r="I15" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="J15" s="38" t="s">
+      <c r="J15" s="10" t="s">
         <v>1032</v>
       </c>
-      <c r="K15" s="38" t="s">
+      <c r="K15" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="28">
         <v>42808</v>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="29">
         <v>45142</v>
       </c>
-      <c r="N15" s="31" t="s">
+      <c r="N15" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11851,19 +11882,19 @@
       <c r="I16" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="J16" s="38" t="s">
+      <c r="J16" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="28">
         <v>43776</v>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="29">
         <v>45142</v>
       </c>
-      <c r="N16" s="31" t="s">
+      <c r="N16" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11895,19 +11926,19 @@
       <c r="I17" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="J17" s="38" t="s">
+      <c r="J17" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="K17" s="38" t="s">
+      <c r="K17" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="28">
         <v>41981</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="29">
         <v>45142</v>
       </c>
-      <c r="N17" s="31" t="s">
+      <c r="N17" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -11942,21 +11973,21 @@
       <c r="J18" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="28">
         <v>42620</v>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="29">
         <v>45142</v>
       </c>
-      <c r="N18" s="31" t="s">
+      <c r="N18" s="30" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="39">
+      <c r="B19" s="10">
         <v>1548</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -11965,10 +11996,10 @@
       <c r="D19" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="10" t="s">
         <v>513</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -11977,22 +12008,22 @@
       <c r="H19" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="10" t="s">
         <v>175</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L19" s="29">
+      <c r="L19" s="28">
         <v>41456</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="29">
         <v>45142</v>
       </c>
-      <c r="N19" s="31"/>
+      <c r="N19" s="30"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
@@ -12022,19 +12053,19 @@
       <c r="I20" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="J20" s="38" t="s">
+      <c r="J20" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="K20" s="38" t="s">
+      <c r="K20" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="28">
         <v>41358</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="29">
         <v>45142</v>
       </c>
-      <c r="N20" s="31" t="s">
+      <c r="N20" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12066,19 +12097,19 @@
       <c r="I21" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="J21" s="38" t="s">
+      <c r="J21" s="10" t="s">
         <v>940</v>
       </c>
-      <c r="K21" s="38" t="s">
+      <c r="K21" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="28">
         <v>41664</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="29">
         <v>45142</v>
       </c>
-      <c r="N21" s="31" t="s">
+      <c r="N21" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12110,19 +12141,19 @@
       <c r="I22" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="J22" s="38" t="s">
+      <c r="J22" s="10" t="s">
         <v>1028</v>
       </c>
-      <c r="K22" s="38" t="s">
+      <c r="K22" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="28">
         <v>42375</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="29">
         <v>45142</v>
       </c>
-      <c r="N22" s="31" t="s">
+      <c r="N22" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12154,19 +12185,19 @@
       <c r="I23" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="J23" s="38" t="s">
+      <c r="J23" s="10" t="s">
         <v>941</v>
       </c>
-      <c r="K23" s="38" t="s">
+      <c r="K23" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="28">
         <v>41640</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="29">
         <v>45142</v>
       </c>
-      <c r="N23" s="31" t="s">
+      <c r="N23" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12198,19 +12229,19 @@
       <c r="I24" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="J24" s="38" t="s">
+      <c r="J24" s="10" t="s">
         <v>1027</v>
       </c>
-      <c r="K24" s="38" t="s">
+      <c r="K24" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="28">
         <v>40857</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="29">
         <v>45142</v>
       </c>
-      <c r="N24" s="31" t="s">
+      <c r="N24" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12242,19 +12273,19 @@
       <c r="I25" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="J25" s="38" t="s">
+      <c r="J25" s="10" t="s">
         <v>1026</v>
       </c>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="28">
         <v>41639</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="29">
         <v>45142</v>
       </c>
-      <c r="N25" s="31" t="s">
+      <c r="N25" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12286,19 +12317,19 @@
       <c r="I26" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J26" s="38" t="s">
+      <c r="J26" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="28">
         <v>42009</v>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="29">
         <v>45142</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12330,19 +12361,19 @@
       <c r="I27" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="J27" s="38" t="s">
+      <c r="J27" s="10" t="s">
         <v>1025</v>
       </c>
-      <c r="K27" s="38" t="s">
+      <c r="K27" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="28">
         <v>41590</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="29">
         <v>45142</v>
       </c>
-      <c r="N27" s="31" t="s">
+      <c r="N27" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12374,19 +12405,19 @@
       <c r="I28" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="J28" s="38" t="s">
+      <c r="J28" s="10" t="s">
         <v>1024</v>
       </c>
-      <c r="K28" s="38" t="s">
+      <c r="K28" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="28">
         <v>42005</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="29">
         <v>45142</v>
       </c>
-      <c r="N28" s="31" t="s">
+      <c r="N28" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12418,19 +12449,19 @@
       <c r="I29" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="J29" s="38" t="s">
+      <c r="J29" s="10" t="s">
         <v>925</v>
       </c>
-      <c r="K29" s="38" t="s">
+      <c r="K29" s="10" t="s">
         <v>934</v>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="28">
         <v>41889</v>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="29">
         <v>45142</v>
       </c>
-      <c r="N29" s="31" t="s">
+      <c r="N29" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12462,19 +12493,19 @@
       <c r="I30" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="J30" s="38" t="s">
+      <c r="J30" s="10" t="s">
         <v>919</v>
       </c>
-      <c r="K30" s="38" t="s">
+      <c r="K30" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="28">
         <v>41794</v>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="29">
         <v>45142</v>
       </c>
-      <c r="N30" s="31" t="s">
+      <c r="N30" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12506,19 +12537,19 @@
       <c r="I31" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="J31" s="38" t="s">
+      <c r="J31" s="10" t="s">
         <v>1023</v>
       </c>
-      <c r="K31" s="38" t="s">
+      <c r="K31" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L31" s="29">
+      <c r="L31" s="28">
         <v>42377</v>
       </c>
-      <c r="M31" s="30">
+      <c r="M31" s="29">
         <v>45142</v>
       </c>
-      <c r="N31" s="31" t="s">
+      <c r="N31" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12553,16 +12584,16 @@
       <c r="J32" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K32" s="38" t="s">
+      <c r="K32" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L32" s="29">
+      <c r="L32" s="28">
         <v>40906</v>
       </c>
-      <c r="M32" s="30">
+      <c r="M32" s="29">
         <v>45142</v>
       </c>
-      <c r="N32" s="31" t="s">
+      <c r="N32" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12597,16 +12628,16 @@
       <c r="J33" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K33" s="38" t="s">
+      <c r="K33" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="28">
         <v>41725</v>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="29">
         <v>45142</v>
       </c>
-      <c r="N33" s="31" t="s">
+      <c r="N33" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12638,17 +12669,17 @@
       <c r="I34" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38" t="s">
+      <c r="J34" s="10"/>
+      <c r="K34" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="28">
         <v>41985</v>
       </c>
-      <c r="M34" s="30">
+      <c r="M34" s="29">
         <v>45142</v>
       </c>
-      <c r="N34" s="31" t="s">
+      <c r="N34" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12680,19 +12711,19 @@
       <c r="I35" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="J35" s="38" t="s">
+      <c r="J35" s="10" t="s">
         <v>1108</v>
       </c>
-      <c r="K35" s="38" t="s">
+      <c r="K35" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="28">
         <v>41985</v>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="29">
         <v>45142</v>
       </c>
-      <c r="N35" s="31" t="s">
+      <c r="N35" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12724,19 +12755,19 @@
       <c r="I36" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="J36" s="38" t="s">
+      <c r="J36" s="10" t="s">
         <v>1003</v>
       </c>
-      <c r="K36" s="38" t="s">
+      <c r="K36" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="28">
         <v>41677</v>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="29">
         <v>45142</v>
       </c>
-      <c r="N36" s="31" t="s">
+      <c r="N36" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12768,19 +12799,19 @@
       <c r="I37" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="J37" s="38" t="s">
+      <c r="J37" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="K37" s="38" t="s">
+      <c r="K37" s="10" t="s">
         <v>934</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="28">
         <v>40857</v>
       </c>
-      <c r="M37" s="30">
+      <c r="M37" s="29">
         <v>45141</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12812,19 +12843,19 @@
       <c r="I38" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="J38" s="38" t="s">
+      <c r="J38" s="10" t="s">
         <v>1012</v>
       </c>
-      <c r="K38" s="38" t="s">
+      <c r="K38" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L38" s="29">
+      <c r="L38" s="28">
         <v>42657</v>
       </c>
-      <c r="M38" s="30">
+      <c r="M38" s="29">
         <v>45141</v>
       </c>
-      <c r="N38" s="31" t="s">
+      <c r="N38" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12856,19 +12887,19 @@
       <c r="I39" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="J39" s="39" t="s">
+      <c r="J39" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="K39" s="38" t="s">
+      <c r="K39" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L39" s="29">
+      <c r="L39" s="28">
         <v>43044</v>
       </c>
-      <c r="M39" s="30">
+      <c r="M39" s="29">
         <v>45141</v>
       </c>
-      <c r="N39" s="31" t="s">
+      <c r="N39" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12900,19 +12931,19 @@
       <c r="I40" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="J40" s="38" t="s">
+      <c r="J40" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="K40" s="38" t="s">
+      <c r="K40" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L40" s="29">
+      <c r="L40" s="28">
         <v>41684</v>
       </c>
-      <c r="M40" s="30">
+      <c r="M40" s="29">
         <v>45141</v>
       </c>
-      <c r="N40" s="31" t="s">
+      <c r="N40" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12947,16 +12978,16 @@
       <c r="J41" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="K41" s="38" t="s">
+      <c r="K41" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L41" s="29">
+      <c r="L41" s="28">
         <v>42678</v>
       </c>
-      <c r="M41" s="30">
+      <c r="M41" s="29">
         <v>45141</v>
       </c>
-      <c r="N41" s="31" t="s">
+      <c r="N41" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -12991,16 +13022,16 @@
       <c r="J42" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="K42" s="38" t="s">
+      <c r="K42" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L42" s="29">
+      <c r="L42" s="28">
         <v>41911</v>
       </c>
-      <c r="M42" s="30">
+      <c r="M42" s="29">
         <v>45141</v>
       </c>
-      <c r="N42" s="31" t="s">
+      <c r="N42" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13035,16 +13066,16 @@
       <c r="J43" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="K43" s="38" t="s">
+      <c r="K43" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L43" s="29">
+      <c r="L43" s="28">
         <v>43508</v>
       </c>
-      <c r="M43" s="30">
+      <c r="M43" s="29">
         <v>45141</v>
       </c>
-      <c r="N43" s="31" t="s">
+      <c r="N43" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13076,19 +13107,19 @@
       <c r="I44" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J44" s="38" t="s">
+      <c r="J44" s="10" t="s">
         <v>998</v>
       </c>
-      <c r="K44" s="38" t="s">
+      <c r="K44" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L44" s="29">
+      <c r="L44" s="28">
         <v>42881</v>
       </c>
-      <c r="M44" s="30">
+      <c r="M44" s="29">
         <v>45141</v>
       </c>
-      <c r="N44" s="31" t="s">
+      <c r="N44" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13123,16 +13154,16 @@
       <c r="J45" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="K45" s="38" t="s">
+      <c r="K45" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="28">
         <v>42432</v>
       </c>
-      <c r="M45" s="30">
+      <c r="M45" s="29">
         <v>45141</v>
       </c>
-      <c r="N45" s="31" t="s">
+      <c r="N45" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13167,16 +13198,16 @@
       <c r="J46" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="K46" s="38" t="s">
+      <c r="K46" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="28">
         <v>42995</v>
       </c>
-      <c r="M46" s="30">
+      <c r="M46" s="29">
         <v>45141</v>
       </c>
-      <c r="N46" s="31" t="s">
+      <c r="N46" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13211,16 +13242,16 @@
       <c r="J47" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="K47" s="38" t="s">
+      <c r="K47" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L47" s="29">
+      <c r="L47" s="28">
         <v>41694</v>
       </c>
-      <c r="M47" s="30">
+      <c r="M47" s="29">
         <v>45141</v>
       </c>
-      <c r="N47" s="31" t="s">
+      <c r="N47" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13255,16 +13286,16 @@
       <c r="J48" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="K48" s="38" t="s">
+      <c r="K48" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L48" s="29">
+      <c r="L48" s="28">
         <v>42552</v>
       </c>
-      <c r="M48" s="30">
+      <c r="M48" s="29">
         <v>45141</v>
       </c>
-      <c r="N48" s="31" t="s">
+      <c r="N48" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13299,16 +13330,16 @@
       <c r="J49" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="K49" s="38" t="s">
+      <c r="K49" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L49" s="29">
+      <c r="L49" s="28">
         <v>41257</v>
       </c>
-      <c r="M49" s="30">
+      <c r="M49" s="29">
         <v>45141</v>
       </c>
-      <c r="N49" s="31" t="s">
+      <c r="N49" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13343,16 +13374,16 @@
       <c r="J50" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="K50" s="38" t="s">
+      <c r="K50" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L50" s="29">
+      <c r="L50" s="28">
         <v>42958</v>
       </c>
-      <c r="M50" s="30">
+      <c r="M50" s="29">
         <v>45141</v>
       </c>
-      <c r="N50" s="31" t="s">
+      <c r="N50" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13387,16 +13418,16 @@
       <c r="J51" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="K51" s="38" t="s">
+      <c r="K51" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L51" s="29">
+      <c r="L51" s="28">
         <v>41275</v>
       </c>
-      <c r="M51" s="30">
+      <c r="M51" s="29">
         <v>45141</v>
       </c>
-      <c r="N51" s="31" t="s">
+      <c r="N51" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13428,19 +13459,19 @@
       <c r="I52" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="J52" s="38" t="s">
+      <c r="J52" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="K52" s="38" t="s">
+      <c r="K52" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L52" s="29">
+      <c r="L52" s="28">
         <v>41866</v>
       </c>
-      <c r="M52" s="30">
+      <c r="M52" s="29">
         <v>45141</v>
       </c>
-      <c r="N52" s="31" t="s">
+      <c r="N52" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13475,16 +13506,16 @@
       <c r="J53" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="K53" s="38" t="s">
+      <c r="K53" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L53" s="29">
+      <c r="L53" s="28">
         <v>41806</v>
       </c>
-      <c r="M53" s="30">
+      <c r="M53" s="29">
         <v>45141</v>
       </c>
-      <c r="N53" s="31" t="s">
+      <c r="N53" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13519,16 +13550,16 @@
       <c r="J54" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="K54" s="38" t="s">
+      <c r="K54" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L54" s="29">
+      <c r="L54" s="28">
         <v>42648</v>
       </c>
-      <c r="M54" s="30">
+      <c r="M54" s="29">
         <v>45142</v>
       </c>
-      <c r="N54" s="31" t="s">
+      <c r="N54" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13563,16 +13594,16 @@
       <c r="J55" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="K55" s="38" t="s">
+      <c r="K55" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L55" s="29">
+      <c r="L55" s="28">
         <v>41640</v>
       </c>
-      <c r="M55" s="30">
+      <c r="M55" s="29">
         <v>45142</v>
       </c>
-      <c r="N55" s="31" t="s">
+      <c r="N55" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13607,16 +13638,16 @@
       <c r="J56" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="K56" s="38" t="s">
+      <c r="K56" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L56" s="29">
+      <c r="L56" s="28">
         <v>41280</v>
       </c>
-      <c r="M56" s="30">
+      <c r="M56" s="29">
         <v>45142</v>
       </c>
-      <c r="N56" s="31" t="s">
+      <c r="N56" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13651,16 +13682,16 @@
       <c r="J57" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="K57" s="38" t="s">
+      <c r="K57" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L57" s="29">
+      <c r="L57" s="28">
         <v>41829</v>
       </c>
-      <c r="M57" s="30">
+      <c r="M57" s="29">
         <v>45142</v>
       </c>
-      <c r="N57" s="31" t="s">
+      <c r="N57" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13695,16 +13726,16 @@
       <c r="J58" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="K58" s="38" t="s">
+      <c r="K58" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L58" s="29">
+      <c r="L58" s="28">
         <v>41045</v>
       </c>
-      <c r="M58" s="30">
+      <c r="M58" s="29">
         <v>45142</v>
       </c>
-      <c r="N58" s="31" t="s">
+      <c r="N58" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13739,16 +13770,16 @@
       <c r="J59" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="K59" s="38" t="s">
+      <c r="K59" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L59" s="29">
+      <c r="L59" s="28">
         <v>41866</v>
       </c>
-      <c r="M59" s="30">
+      <c r="M59" s="29">
         <v>45142</v>
       </c>
-      <c r="N59" s="31" t="s">
+      <c r="N59" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13783,16 +13814,16 @@
       <c r="J60" s="5" t="s">
         <v>920</v>
       </c>
-      <c r="K60" s="38" t="s">
+      <c r="K60" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L60" s="29">
+      <c r="L60" s="28">
         <v>41035</v>
       </c>
-      <c r="M60" s="30">
+      <c r="M60" s="29">
         <v>45142</v>
       </c>
-      <c r="N60" s="31" t="s">
+      <c r="N60" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13827,16 +13858,16 @@
       <c r="J61" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="K61" s="38" t="s">
+      <c r="K61" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L61" s="29">
+      <c r="L61" s="28">
         <v>41511</v>
       </c>
-      <c r="M61" s="30">
+      <c r="M61" s="29">
         <v>45142</v>
       </c>
-      <c r="N61" s="31" t="s">
+      <c r="N61" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13871,16 +13902,16 @@
       <c r="J62" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="K62" s="38" t="s">
+      <c r="K62" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L62" s="29">
+      <c r="L62" s="28">
         <v>42022</v>
       </c>
-      <c r="M62" s="30">
+      <c r="M62" s="29">
         <v>45142</v>
       </c>
-      <c r="N62" s="31" t="s">
+      <c r="N62" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13912,19 +13943,19 @@
       <c r="I63" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="J63" s="38" t="s">
+      <c r="J63" s="10" t="s">
         <v>1109</v>
       </c>
-      <c r="K63" s="38" t="s">
+      <c r="K63" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L63" s="29">
+      <c r="L63" s="28">
         <v>41667</v>
       </c>
-      <c r="M63" s="30">
+      <c r="M63" s="29">
         <v>45142</v>
       </c>
-      <c r="N63" s="31" t="s">
+      <c r="N63" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -13959,16 +13990,16 @@
       <c r="J64" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="K64" s="38" t="s">
+      <c r="K64" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L64" s="29">
+      <c r="L64" s="28">
         <v>41640</v>
       </c>
-      <c r="M64" s="30">
+      <c r="M64" s="29">
         <v>45142</v>
       </c>
-      <c r="N64" s="31" t="s">
+      <c r="N64" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14000,19 +14031,19 @@
       <c r="I65" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="38" t="s">
+      <c r="J65" s="10" t="s">
         <v>989</v>
       </c>
-      <c r="K65" s="38" t="s">
+      <c r="K65" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L65" s="29">
+      <c r="L65" s="28">
         <v>41671</v>
       </c>
-      <c r="M65" s="30">
+      <c r="M65" s="29">
         <v>45142</v>
       </c>
-      <c r="N65" s="31" t="s">
+      <c r="N65" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14047,16 +14078,16 @@
       <c r="J66" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="K66" s="38" t="s">
+      <c r="K66" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L66" s="29">
+      <c r="L66" s="28">
         <v>41122</v>
       </c>
-      <c r="M66" s="30">
+      <c r="M66" s="29">
         <v>45142</v>
       </c>
-      <c r="N66" s="31" t="s">
+      <c r="N66" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14088,17 +14119,17 @@
       <c r="I67" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38" t="s">
+      <c r="J67" s="10"/>
+      <c r="K67" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L67" s="29">
+      <c r="L67" s="28">
         <v>41802</v>
       </c>
-      <c r="M67" s="30">
+      <c r="M67" s="29">
         <v>45142</v>
       </c>
-      <c r="N67" s="31" t="s">
+      <c r="N67" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14133,16 +14164,16 @@
       <c r="J68" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="K68" s="38" t="s">
+      <c r="K68" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L68" s="29">
+      <c r="L68" s="28">
         <v>41456</v>
       </c>
-      <c r="M68" s="30">
+      <c r="M68" s="29">
         <v>45142</v>
       </c>
-      <c r="N68" s="31" t="s">
+      <c r="N68" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14177,16 +14208,16 @@
       <c r="J69" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="K69" s="38" t="s">
+      <c r="K69" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L69" s="29">
+      <c r="L69" s="28">
         <v>42370</v>
       </c>
-      <c r="M69" s="30">
+      <c r="M69" s="29">
         <v>45142</v>
       </c>
-      <c r="N69" s="31" t="s">
+      <c r="N69" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14221,16 +14252,16 @@
       <c r="J70" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="K70" s="38" t="s">
+      <c r="K70" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L70" s="29">
+      <c r="L70" s="28">
         <v>41495</v>
       </c>
-      <c r="M70" s="30">
+      <c r="M70" s="29">
         <v>45142</v>
       </c>
-      <c r="N70" s="31" t="s">
+      <c r="N70" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14265,16 +14296,16 @@
       <c r="J71" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="K71" s="38" t="s">
+      <c r="K71" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L71" s="29">
+      <c r="L71" s="28">
         <v>41349</v>
       </c>
-      <c r="M71" s="30">
+      <c r="M71" s="29">
         <v>45142</v>
       </c>
-      <c r="N71" s="31" t="s">
+      <c r="N71" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14309,16 +14340,16 @@
       <c r="J72" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="K72" s="38" t="s">
+      <c r="K72" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L72" s="29">
+      <c r="L72" s="28">
         <v>42756</v>
       </c>
-      <c r="M72" s="30">
+      <c r="M72" s="29">
         <v>45142</v>
       </c>
-      <c r="N72" s="31" t="s">
+      <c r="N72" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14353,16 +14384,16 @@
       <c r="J73" s="5" t="s">
         <v>954</v>
       </c>
-      <c r="K73" s="38" t="s">
+      <c r="K73" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L73" s="29">
+      <c r="L73" s="28">
         <v>42370</v>
       </c>
-      <c r="M73" s="30">
+      <c r="M73" s="29">
         <v>45142</v>
       </c>
-      <c r="N73" s="31" t="s">
+      <c r="N73" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14397,16 +14428,16 @@
       <c r="J74" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="K74" s="38" t="s">
+      <c r="K74" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L74" s="29">
+      <c r="L74" s="28">
         <v>41235</v>
       </c>
-      <c r="M74" s="30">
+      <c r="M74" s="29">
         <v>45142</v>
       </c>
-      <c r="N74" s="31" t="s">
+      <c r="N74" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14438,19 +14469,19 @@
       <c r="I75" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="J75" s="38" t="s">
+      <c r="J75" s="10" t="s">
         <v>1034</v>
       </c>
-      <c r="K75" s="38" t="s">
+      <c r="K75" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L75" s="29">
+      <c r="L75" s="28">
         <v>42063</v>
       </c>
-      <c r="M75" s="30">
+      <c r="M75" s="29">
         <v>45142</v>
       </c>
-      <c r="N75" s="31" t="s">
+      <c r="N75" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14482,19 +14513,19 @@
       <c r="I76" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="J76" s="38" t="s">
+      <c r="J76" s="10" t="s">
         <v>1110</v>
       </c>
-      <c r="K76" s="38" t="s">
+      <c r="K76" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L76" s="30">
+      <c r="L76" s="29">
         <v>42505</v>
       </c>
-      <c r="M76" s="30">
+      <c r="M76" s="29">
         <v>45143</v>
       </c>
-      <c r="N76" s="31" t="s">
+      <c r="N76" s="30" t="s">
         <v>320</v>
       </c>
     </row>
@@ -14526,57 +14557,57 @@
       <c r="I77" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="J77" s="38" t="s">
+      <c r="J77" s="10" t="s">
         <v>1002</v>
       </c>
-      <c r="K77" s="38" t="s">
+      <c r="K77" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="L77" s="30">
+      <c r="L77" s="29">
         <v>39457</v>
       </c>
-      <c r="M77" s="30">
+      <c r="M77" s="29">
         <v>45143</v>
       </c>
-      <c r="N77" s="31" t="s">
+      <c r="N77" s="30" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="62" t="s">
+      <c r="A79" s="55" t="s">
         <v>607</v>
       </c>
-      <c r="B79" s="63"/>
-      <c r="C79" s="63"/>
-      <c r="D79" s="63"/>
-      <c r="E79" s="63"/>
-      <c r="F79" s="63"/>
-      <c r="G79" s="63"/>
-      <c r="H79" s="63"/>
-      <c r="I79" s="63"/>
-      <c r="J79" s="63"/>
-      <c r="K79" s="63"/>
-      <c r="L79" s="63"/>
-      <c r="M79" s="63"/>
-      <c r="N79" s="63"/>
-      <c r="O79" s="64"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="56"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="56"/>
+      <c r="K79" s="56"/>
+      <c r="L79" s="56"/>
+      <c r="M79" s="56"/>
+      <c r="N79" s="56"/>
+      <c r="O79" s="57"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A80" s="65"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="66"/>
-      <c r="K80" s="66"/>
-      <c r="L80" s="66"/>
-      <c r="M80" s="66"/>
-      <c r="N80" s="66"/>
-      <c r="O80" s="67"/>
+      <c r="A80" s="58"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
+      <c r="J80" s="59"/>
+      <c r="K80" s="59"/>
+      <c r="L80" s="59"/>
+      <c r="M80" s="59"/>
+      <c r="N80" s="59"/>
+      <c r="O80" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -14604,7 +14635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14615,7 +14646,8 @@
     <col min="2" max="2" width="12.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="26.140625" style="5" customWidth="1"/>
     <col min="4" max="4" width="19.140625" style="5" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="5"/>
+    <col min="5" max="5" width="9.140625" style="5"/>
+    <col min="6" max="6" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="21.28515625" style="5" customWidth="1"/>
     <col min="9" max="9" width="12" style="5" customWidth="1"/>
@@ -14627,260 +14659,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>603</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="64"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="57"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="74"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="67"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="74"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="67"/>
     </row>
     <row r="4" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="74"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="67"/>
     </row>
     <row r="5" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="74"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="67"/>
     </row>
     <row r="6" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="73"/>
-      <c r="Q6" s="74"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="67"/>
     </row>
     <row r="7" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="74"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="67"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="66"/>
-      <c r="N8" s="66"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="67"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="59"/>
+      <c r="P8" s="59"/>
+      <c r="Q8" s="60"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="68" t="s">
         <v>604</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="27"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="26"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="66"/>
-      <c r="K10" s="66"/>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="27"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="52" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="59" t="s">
+      <c r="I11" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="59" t="s">
+      <c r="J11" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="K11" s="69" t="s">
+      <c r="K11" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="60" t="s">
+      <c r="L11" s="53" t="s">
         <v>878</v>
       </c>
-      <c r="M11" s="60" t="s">
+      <c r="M11" s="53" t="s">
         <v>753</v>
       </c>
-      <c r="N11" s="69" t="s">
+      <c r="N11" s="62" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="69"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="62"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
@@ -14916,13 +14948,13 @@
       <c r="K13" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="38" t="s">
+      <c r="L13" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="M13" s="38" t="s">
+      <c r="M13" s="10" t="s">
         <v>1093</v>
       </c>
-      <c r="N13" s="33" t="s">
+      <c r="N13" s="10" t="s">
         <v>514</v>
       </c>
     </row>
@@ -14960,10 +14992,10 @@
       <c r="K14" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="38" t="s">
+      <c r="L14" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="M14" s="50" t="s">
+      <c r="M14" s="10" t="s">
         <v>1093</v>
       </c>
       <c r="N14" s="10" t="s">
@@ -15004,10 +15036,10 @@
       <c r="K15" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="L15" s="38" t="s">
+      <c r="L15" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="M15" s="38" t="s">
+      <c r="M15" s="10" t="s">
         <v>931</v>
       </c>
       <c r="N15" s="10" t="s">
@@ -15048,10 +15080,10 @@
       <c r="K16" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="L16" s="38" t="s">
+      <c r="L16" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M16" s="38" t="s">
+      <c r="M16" s="10" t="s">
         <v>1022</v>
       </c>
       <c r="N16" s="10" t="s">
@@ -15092,10 +15124,10 @@
       <c r="K17" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="L17" s="38" t="s">
+      <c r="L17" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="M17" s="38" t="s">
+      <c r="M17" s="10" t="s">
         <v>1094</v>
       </c>
       <c r="N17" s="10" t="s">
@@ -15136,10 +15168,10 @@
       <c r="K18" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="M18" s="38" t="s">
+      <c r="M18" s="10" t="s">
         <v>1021</v>
       </c>
       <c r="N18" s="10" t="s">
@@ -15180,10 +15212,10 @@
       <c r="K19" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="L19" s="38" t="s">
+      <c r="L19" s="10" t="s">
         <v>891</v>
       </c>
-      <c r="M19" s="38" t="s">
+      <c r="M19" s="10" t="s">
         <v>954</v>
       </c>
       <c r="N19" s="10" t="s">
@@ -15224,7 +15256,7 @@
       <c r="K20" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="L20" s="38" t="s">
+      <c r="L20" s="10" t="s">
         <v>883</v>
       </c>
       <c r="M20" s="5" t="s">
@@ -15268,10 +15300,10 @@
       <c r="K21" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="L21" s="38" t="s">
+      <c r="L21" s="10" t="s">
         <v>904</v>
       </c>
-      <c r="M21" s="38" t="s">
+      <c r="M21" s="10" t="s">
         <v>982</v>
       </c>
       <c r="N21" s="10" t="s">
@@ -15312,10 +15344,10 @@
       <c r="K22" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="L22" s="38" t="s">
+      <c r="L22" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M22" s="38" t="s">
+      <c r="M22" s="10" t="s">
         <v>1020</v>
       </c>
       <c r="N22" s="10" t="s">
@@ -15356,10 +15388,10 @@
       <c r="K23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L23" s="38" t="s">
+      <c r="L23" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="M23" s="38" t="s">
+      <c r="M23" s="10" t="s">
         <v>693</v>
       </c>
       <c r="N23" s="10" t="s">
@@ -15400,10 +15432,10 @@
       <c r="K24" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="L24" s="38" t="s">
+      <c r="L24" s="10" t="s">
         <v>906</v>
       </c>
-      <c r="M24" s="39" t="s">
+      <c r="M24" s="10" t="s">
         <v>1019</v>
       </c>
       <c r="N24" s="10" t="s">
@@ -15444,10 +15476,10 @@
       <c r="K25" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="L25" s="38" t="s">
+      <c r="L25" s="10" t="s">
         <v>906</v>
       </c>
-      <c r="M25" s="38" t="s">
+      <c r="M25" s="10" t="s">
         <v>1019</v>
       </c>
       <c r="N25" s="10" t="s">
@@ -15488,7 +15520,7 @@
       <c r="K26" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="L26" s="38" t="s">
+      <c r="L26" s="10" t="s">
         <v>901</v>
       </c>
       <c r="M26" s="5" t="s">
@@ -15532,7 +15564,7 @@
       <c r="K27" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="L27" s="38" t="s">
+      <c r="L27" s="10" t="s">
         <v>901</v>
       </c>
       <c r="M27" s="5" t="s">
@@ -15576,10 +15608,10 @@
       <c r="K28" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="L28" s="38" t="s">
+      <c r="L28" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M28" s="38" t="s">
+      <c r="M28" s="10" t="s">
         <v>1018</v>
       </c>
       <c r="N28" s="10" t="s">
@@ -15620,10 +15652,10 @@
       <c r="K29" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="L29" s="38" t="s">
+      <c r="L29" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M29" s="38" t="s">
+      <c r="M29" s="10" t="s">
         <v>1004</v>
       </c>
       <c r="N29" s="10" t="s">
@@ -15664,10 +15696,10 @@
       <c r="K30" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L30" s="38" t="s">
+      <c r="L30" s="10" t="s">
         <v>907</v>
       </c>
-      <c r="M30" s="38" t="s">
+      <c r="M30" s="10" t="s">
         <v>1017</v>
       </c>
       <c r="N30" s="10" t="s">
@@ -15708,10 +15740,10 @@
       <c r="K31" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="L31" s="38" t="s">
+      <c r="L31" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M31" s="38" t="s">
+      <c r="M31" s="10" t="s">
         <v>736</v>
       </c>
       <c r="N31" s="10" t="s">
@@ -15752,10 +15784,10 @@
       <c r="K32" s="10" t="s">
         <v>523</v>
       </c>
-      <c r="L32" s="38" t="s">
+      <c r="L32" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M32" s="38" t="s">
+      <c r="M32" s="10" t="s">
         <v>736</v>
       </c>
       <c r="N32" s="10" t="s">
@@ -15796,10 +15828,10 @@
       <c r="K33" s="10" t="s">
         <v>1079</v>
       </c>
-      <c r="L33" s="38" t="s">
+      <c r="L33" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M33" s="38" t="s">
+      <c r="M33" s="10" t="s">
         <v>1016</v>
       </c>
       <c r="N33" s="10" t="s">
@@ -15840,10 +15872,10 @@
       <c r="K34" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="L34" s="38" t="s">
+      <c r="L34" s="10" t="s">
         <v>901</v>
       </c>
-      <c r="M34" s="38" t="s">
+      <c r="M34" s="10" t="s">
         <v>886</v>
       </c>
       <c r="N34" s="10" t="s">
@@ -15884,10 +15916,10 @@
       <c r="K35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L35" s="38" t="s">
+      <c r="L35" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="M35" s="38" t="s">
+      <c r="M35" s="10" t="s">
         <v>693</v>
       </c>
       <c r="N35" s="10" t="s">
@@ -15928,10 +15960,10 @@
       <c r="K36" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="L36" s="38" t="s">
+      <c r="L36" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M36" s="38" t="s">
+      <c r="M36" s="10" t="s">
         <v>1015</v>
       </c>
       <c r="N36" s="10" t="s">
@@ -15972,10 +16004,10 @@
       <c r="K37" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="L37" s="38" t="s">
+      <c r="L37" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M37" s="38" t="s">
+      <c r="M37" s="10" t="s">
         <v>1014</v>
       </c>
       <c r="N37" s="10" t="s">
@@ -16016,10 +16048,10 @@
       <c r="K38" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="L38" s="38" t="s">
+      <c r="L38" s="10" t="s">
         <v>845</v>
       </c>
-      <c r="M38" s="38" t="s">
+      <c r="M38" s="10" t="s">
         <v>1013</v>
       </c>
       <c r="N38" s="10" t="s">
@@ -16060,7 +16092,7 @@
       <c r="K39" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="L39" s="38" t="s">
+      <c r="L39" s="10" t="s">
         <v>883</v>
       </c>
       <c r="M39" s="5" t="s">
@@ -16104,7 +16136,7 @@
       <c r="K40" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="L40" s="38" t="s">
+      <c r="L40" s="10" t="s">
         <v>883</v>
       </c>
       <c r="M40" s="5" t="s">
@@ -16148,10 +16180,10 @@
       <c r="K41" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="L41" s="38" t="s">
+      <c r="L41" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M41" s="38" t="s">
+      <c r="M41" s="10" t="s">
         <v>1012</v>
       </c>
       <c r="N41" s="10" t="s">
@@ -16192,10 +16224,10 @@
       <c r="K42" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L42" s="38" t="s">
+      <c r="L42" s="10" t="s">
         <v>853</v>
       </c>
-      <c r="M42" s="38" t="s">
+      <c r="M42" s="10" t="s">
         <v>999</v>
       </c>
       <c r="N42" s="10" t="s">
@@ -16236,10 +16268,10 @@
       <c r="K43" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="L43" s="38" t="s">
+      <c r="L43" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M43" s="38" t="s">
+      <c r="M43" s="10" t="s">
         <v>1011</v>
       </c>
       <c r="N43" s="10" t="s">
@@ -16280,10 +16312,10 @@
       <c r="K44" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L44" s="38" t="s">
+      <c r="L44" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M44" s="38" t="s">
+      <c r="M44" s="10" t="s">
         <v>1010</v>
       </c>
       <c r="N44" s="10" t="s">
@@ -16324,10 +16356,10 @@
       <c r="K45" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="L45" s="38" t="s">
+      <c r="L45" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M45" s="38" t="s">
+      <c r="M45" s="10" t="s">
         <v>1009</v>
       </c>
       <c r="N45" s="10" t="s">
@@ -16368,10 +16400,10 @@
       <c r="K46" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="L46" s="38" t="s">
+      <c r="L46" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M46" s="38" t="s">
+      <c r="M46" s="10" t="s">
         <v>1008</v>
       </c>
       <c r="N46" s="10" t="s">
@@ -16412,10 +16444,10 @@
       <c r="K47" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="L47" s="38" t="s">
+      <c r="L47" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M47" s="38" t="s">
+      <c r="M47" s="10" t="s">
         <v>1007</v>
       </c>
       <c r="N47" s="10" t="s">
@@ -16456,10 +16488,10 @@
       <c r="K48" s="10" t="s">
         <v>532</v>
       </c>
-      <c r="L48" s="38" t="s">
+      <c r="L48" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M48" s="38" t="s">
+      <c r="M48" s="10" t="s">
         <v>1006</v>
       </c>
       <c r="N48" s="10" t="s">
@@ -16500,10 +16532,10 @@
       <c r="K49" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="L49" s="38" t="s">
+      <c r="L49" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="M49" s="38" t="s">
+      <c r="M49" s="10" t="s">
         <v>1005</v>
       </c>
       <c r="N49" s="10" t="s">
@@ -16519,41 +16551,41 @@
       <c r="A51" s="5">
         <v>39</v>
       </c>
-      <c r="B51" s="62" t="s">
+      <c r="B51" s="55" t="s">
         <v>607</v>
       </c>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="63"/>
-      <c r="O51" s="64"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="57"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>40</v>
       </c>
-      <c r="B52" s="65"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="66"/>
-      <c r="I52" s="66"/>
-      <c r="J52" s="66"/>
-      <c r="K52" s="66"/>
-      <c r="L52" s="66"/>
-      <c r="M52" s="66"/>
-      <c r="N52" s="66"/>
-      <c r="O52" s="67"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="60"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
@@ -16747,7 +16779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16770,176 +16802,176 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="61" t="s">
         <v>603</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="61"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="61"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="63" t="s">
         <v>313</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="59" t="s">
+      <c r="J7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="69" t="s">
+      <c r="L7" s="62" t="s">
         <v>11</v>
       </c>
       <c r="M7" s="5" t="s">
@@ -16950,20 +16982,20 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="32" t="s">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="69"/>
+      <c r="L8" s="62"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
@@ -16981,16 +17013,16 @@
       <c r="E9" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>42409</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>44775</v>
       </c>
       <c r="K9" s="5">
@@ -17022,16 +17054,16 @@
       <c r="E10" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="29">
         <v>41451</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="29">
         <v>44775</v>
       </c>
       <c r="K10" s="5">
@@ -17063,16 +17095,16 @@
       <c r="E11" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G11" s="39" t="s">
+      <c r="G11" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="29">
         <v>42496</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="29">
         <v>44775</v>
       </c>
       <c r="K11" s="5">
@@ -17104,16 +17136,16 @@
       <c r="E12" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="29">
         <v>42165</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="29">
         <v>44775</v>
       </c>
       <c r="K12" s="5">
@@ -17145,16 +17177,16 @@
       <c r="E13" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="29">
         <v>42005</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="29">
         <v>44775</v>
       </c>
       <c r="K13" s="5">
@@ -17186,16 +17218,16 @@
       <c r="E14" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="29">
         <v>41202</v>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="29">
         <v>44778</v>
       </c>
       <c r="K14" s="5">
@@ -17221,16 +17253,16 @@
       <c r="E15" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="29">
         <v>41383</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="29">
         <v>44778</v>
       </c>
       <c r="K15" s="5">
@@ -17262,16 +17294,16 @@
       <c r="E16" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="29">
         <v>41143</v>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="29">
         <v>44778</v>
       </c>
       <c r="K16" s="5">
@@ -17297,16 +17329,16 @@
       <c r="E17" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="29">
         <v>42301</v>
       </c>
-      <c r="J17" s="30">
+      <c r="J17" s="29">
         <v>44778</v>
       </c>
       <c r="K17" s="5">
@@ -17332,16 +17364,16 @@
       <c r="E18" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="29">
         <v>41553</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="29">
         <v>44778</v>
       </c>
       <c r="K18" s="5">
@@ -17373,16 +17405,16 @@
       <c r="E19" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="29">
         <v>42006</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="29">
         <v>44778</v>
       </c>
       <c r="K19" s="5">
@@ -17411,16 +17443,16 @@
       <c r="E20" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="29">
         <v>41495</v>
       </c>
-      <c r="J20" s="30">
+      <c r="J20" s="29">
         <v>44778</v>
       </c>
       <c r="K20" s="5">
@@ -17449,7 +17481,7 @@
       <c r="E21" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="10" t="s">
         <v>534</v>
       </c>
       <c r="K21" s="5">
@@ -17475,16 +17507,16 @@
       <c r="E22" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="29">
         <v>41561</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="29">
         <v>44788</v>
       </c>
       <c r="K22" s="5">
@@ -17516,16 +17548,16 @@
       <c r="E23" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="G23" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="29">
         <v>41860</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="29">
         <v>44789</v>
       </c>
       <c r="K23" s="5">
@@ -17551,16 +17583,16 @@
       <c r="E24" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="29">
         <v>41253</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="29">
         <v>44789</v>
       </c>
       <c r="K24" s="5">
@@ -17592,16 +17624,16 @@
       <c r="E25" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G25" s="39" t="s">
+      <c r="G25" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="29">
         <v>40374</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="29">
         <v>44789</v>
       </c>
       <c r="K25" s="5">
@@ -17633,16 +17665,16 @@
       <c r="E26" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G26" s="39" t="s">
+      <c r="G26" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="29">
         <v>42531</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J26" s="29">
         <v>44789</v>
       </c>
       <c r="K26" s="5">
@@ -17674,16 +17706,16 @@
       <c r="E27" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="29">
         <v>41713</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="29">
         <v>44796</v>
       </c>
       <c r="K27" s="5">
@@ -17712,16 +17744,16 @@
       <c r="E28" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G28" s="39" t="s">
+      <c r="G28" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="29">
         <v>41641</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="29">
         <v>44796</v>
       </c>
       <c r="K28" s="5">
@@ -17753,16 +17785,16 @@
       <c r="E29" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G29" s="39" t="s">
+      <c r="G29" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>707</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="29">
         <v>41011</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="29">
         <v>44796</v>
       </c>
       <c r="K29" s="5">
@@ -17794,16 +17826,16 @@
       <c r="E30" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="29">
         <v>41706</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="29">
         <v>44796</v>
       </c>
       <c r="K30" s="5">
@@ -17835,16 +17867,16 @@
       <c r="E31" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G31" s="39" t="s">
+      <c r="G31" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="29">
         <v>41730</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="29">
         <v>44796</v>
       </c>
       <c r="K31" s="5">
@@ -17876,16 +17908,16 @@
       <c r="E32" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="29">
         <v>41734</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="29">
         <v>44796</v>
       </c>
       <c r="K32" s="5">
@@ -17911,16 +17943,16 @@
       <c r="E33" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G33" s="39" t="s">
+      <c r="G33" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="29">
         <v>42019</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="29">
         <v>44796</v>
       </c>
       <c r="K33" s="5">
@@ -17952,16 +17984,16 @@
       <c r="E34" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="29">
         <v>42301</v>
       </c>
-      <c r="J34" s="30">
+      <c r="J34" s="29">
         <v>44796</v>
       </c>
       <c r="K34" s="5">
@@ -17993,16 +18025,16 @@
       <c r="E35" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G35" s="39" t="s">
+      <c r="G35" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I35" s="30">
+      <c r="I35" s="29">
         <v>42474</v>
       </c>
-      <c r="J35" s="30">
+      <c r="J35" s="29">
         <v>44796</v>
       </c>
       <c r="K35" s="5">
@@ -18034,16 +18066,16 @@
       <c r="E36" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="I36" s="30">
+      <c r="I36" s="29">
         <v>42571</v>
       </c>
-      <c r="J36" s="30">
+      <c r="J36" s="29">
         <v>44796</v>
       </c>
       <c r="K36" s="5">
@@ -18069,16 +18101,16 @@
       <c r="E37" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G37" s="39" t="s">
+      <c r="G37" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I37" s="30">
+      <c r="I37" s="29">
         <v>41795</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="29">
         <v>44796</v>
       </c>
       <c r="K37" s="5">
@@ -18110,16 +18142,16 @@
       <c r="E38" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="I38" s="30">
+      <c r="I38" s="29">
         <v>41690</v>
       </c>
-      <c r="J38" s="30">
+      <c r="J38" s="29">
         <v>44796</v>
       </c>
       <c r="K38" s="5">
@@ -18151,16 +18183,16 @@
       <c r="E39" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G39" s="39" t="s">
+      <c r="G39" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="29">
         <v>40867</v>
       </c>
-      <c r="J39" s="30">
+      <c r="J39" s="29">
         <v>44796</v>
       </c>
       <c r="K39" s="5">
@@ -18192,7 +18224,7 @@
       <c r="E40" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G40" s="39" t="s">
+      <c r="G40" s="10" t="s">
         <v>534</v>
       </c>
       <c r="K40" s="5">
@@ -18218,16 +18250,16 @@
       <c r="E41" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="I41" s="30">
+      <c r="I41" s="29">
         <v>42005</v>
       </c>
-      <c r="J41" s="30">
+      <c r="J41" s="29">
         <v>44805</v>
       </c>
       <c r="K41" s="5">
@@ -18253,16 +18285,16 @@
       <c r="E42" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G42" s="39" t="s">
+      <c r="G42" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="I42" s="30">
+      <c r="I42" s="29">
         <v>41315</v>
       </c>
-      <c r="J42" s="30">
+      <c r="J42" s="29">
         <v>44886</v>
       </c>
       <c r="K42" s="5">
@@ -18294,16 +18326,16 @@
       <c r="E43" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G43" s="39" t="s">
+      <c r="G43" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="I43" s="30">
+      <c r="I43" s="29">
         <v>40536</v>
       </c>
-      <c r="J43" s="30">
+      <c r="J43" s="29">
         <v>44783</v>
       </c>
       <c r="K43" s="5">
@@ -18335,16 +18367,16 @@
       <c r="E44" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G44" s="39" t="s">
+      <c r="G44" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="I44" s="30">
+      <c r="I44" s="29">
         <v>41325</v>
       </c>
-      <c r="J44" s="30">
+      <c r="J44" s="29">
         <v>44783</v>
       </c>
       <c r="K44" s="5">
@@ -18376,16 +18408,16 @@
       <c r="E45" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G45" s="39" t="s">
+      <c r="G45" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="I45" s="30">
+      <c r="I45" s="29">
         <v>41703</v>
       </c>
-      <c r="J45" s="30">
+      <c r="J45" s="29">
         <v>44783</v>
       </c>
       <c r="K45" s="5">
@@ -18414,16 +18446,16 @@
       <c r="E46" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G46" s="39" t="s">
+      <c r="G46" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="30">
+      <c r="I46" s="29">
         <v>42045</v>
       </c>
-      <c r="J46" s="30">
+      <c r="J46" s="29">
         <v>44786</v>
       </c>
       <c r="K46" s="5">
@@ -18455,16 +18487,16 @@
       <c r="E47" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G47" s="39" t="s">
+      <c r="G47" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="I47" s="30">
+      <c r="I47" s="29">
         <v>40944</v>
       </c>
-      <c r="J47" s="30">
+      <c r="J47" s="29">
         <v>44786</v>
       </c>
       <c r="K47" s="5">
@@ -18496,16 +18528,16 @@
       <c r="E48" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G48" s="39" t="s">
+      <c r="G48" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="I48" s="30">
+      <c r="I48" s="29">
         <v>41710</v>
       </c>
-      <c r="J48" s="30">
+      <c r="J48" s="29">
         <v>44786</v>
       </c>
       <c r="K48" s="5">
@@ -18537,16 +18569,16 @@
       <c r="E49" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G49" s="39" t="s">
+      <c r="G49" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="I49" s="30">
+      <c r="I49" s="29">
         <v>41100</v>
       </c>
-      <c r="J49" s="30">
+      <c r="J49" s="29">
         <v>44786</v>
       </c>
       <c r="K49" s="5">
@@ -18578,16 +18610,16 @@
       <c r="E50" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G50" s="39" t="s">
+      <c r="G50" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="I50" s="30">
+      <c r="I50" s="29">
         <v>42190</v>
       </c>
-      <c r="J50" s="30">
+      <c r="J50" s="29">
         <v>44786</v>
       </c>
       <c r="K50" s="5">
@@ -18613,16 +18645,16 @@
       <c r="E51" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G51" s="39" t="s">
+      <c r="G51" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="I51" s="30">
+      <c r="I51" s="29">
         <v>41414</v>
       </c>
-      <c r="J51" s="30">
+      <c r="J51" s="29">
         <v>44786</v>
       </c>
       <c r="K51" s="5">
@@ -18654,16 +18686,16 @@
       <c r="E52" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G52" s="39" t="s">
+      <c r="G52" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="I52" s="30">
+      <c r="I52" s="29">
         <v>41284</v>
       </c>
-      <c r="J52" s="30">
+      <c r="J52" s="29">
         <v>44786</v>
       </c>
       <c r="K52" s="5">
@@ -18689,16 +18721,16 @@
       <c r="E53" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="G53" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="I53" s="30">
+      <c r="I53" s="29">
         <v>40704</v>
       </c>
-      <c r="J53" s="30">
+      <c r="J53" s="29">
         <v>44796</v>
       </c>
       <c r="K53" s="5">
@@ -18730,16 +18762,16 @@
       <c r="E54" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="G54" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="I54" s="30">
+      <c r="I54" s="29">
         <v>41640</v>
       </c>
-      <c r="J54" s="30">
+      <c r="J54" s="29">
         <v>44802</v>
       </c>
       <c r="K54" s="5">
@@ -18771,16 +18803,16 @@
       <c r="E55" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G55" s="39" t="s">
+      <c r="G55" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="I55" s="30">
+      <c r="I55" s="29">
         <v>43439</v>
       </c>
-      <c r="J55" s="30">
+      <c r="J55" s="29">
         <v>44802</v>
       </c>
       <c r="K55" s="5">
@@ -18812,16 +18844,16 @@
       <c r="E56" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G56" s="39" t="s">
+      <c r="G56" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="I56" s="30">
+      <c r="I56" s="29">
         <v>40887</v>
       </c>
-      <c r="J56" s="30">
+      <c r="J56" s="29">
         <v>44802</v>
       </c>
       <c r="K56" s="5">
@@ -18850,16 +18882,16 @@
       <c r="E57" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="I57" s="30">
+      <c r="I57" s="29">
         <v>42767</v>
       </c>
-      <c r="J57" s="30">
+      <c r="J57" s="29">
         <v>44802</v>
       </c>
       <c r="K57" s="5">
@@ -18891,16 +18923,16 @@
       <c r="E58" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G58" s="39" t="s">
+      <c r="G58" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="I58" s="30">
+      <c r="I58" s="29">
         <v>40123</v>
       </c>
-      <c r="J58" s="30">
+      <c r="J58" s="29">
         <v>44802</v>
       </c>
       <c r="K58" s="5">
@@ -18932,16 +18964,16 @@
       <c r="E59" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="G59" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="I59" s="30">
+      <c r="I59" s="29">
         <v>41528</v>
       </c>
-      <c r="J59" s="30">
+      <c r="J59" s="29">
         <v>44802</v>
       </c>
       <c r="K59" s="5">
@@ -18967,16 +18999,16 @@
       <c r="E60" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G60" s="39" t="s">
+      <c r="G60" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="I60" s="30">
+      <c r="I60" s="29">
         <v>40979</v>
       </c>
-      <c r="J60" s="30">
+      <c r="J60" s="29">
         <v>44802</v>
       </c>
       <c r="K60" s="5">
@@ -19008,16 +19040,16 @@
       <c r="E61" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G61" s="39" t="s">
+      <c r="G61" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="I61" s="30">
+      <c r="I61" s="29">
         <v>41271</v>
       </c>
-      <c r="J61" s="30">
+      <c r="J61" s="29">
         <v>44802</v>
       </c>
       <c r="K61" s="5">
@@ -19046,7 +19078,7 @@
       <c r="E62" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G62" s="39" t="s">
+      <c r="G62" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H62" s="5" t="s">
@@ -19078,16 +19110,16 @@
       <c r="E63" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G63" s="39" t="s">
+      <c r="G63" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="I63" s="30">
+      <c r="I63" s="29">
         <v>41093</v>
       </c>
-      <c r="J63" s="30">
+      <c r="J63" s="29">
         <v>44805</v>
       </c>
       <c r="K63" s="5">
@@ -19113,16 +19145,16 @@
       <c r="E64" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G64" s="39" t="s">
+      <c r="G64" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="I64" s="30">
+      <c r="I64" s="29">
         <v>41135</v>
       </c>
-      <c r="J64" s="30">
+      <c r="J64" s="29">
         <v>44805</v>
       </c>
       <c r="K64" s="5">
@@ -19154,7 +19186,7 @@
       <c r="E65" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="G65" s="10" t="s">
         <v>534</v>
       </c>
       <c r="K65" s="5">
@@ -19186,16 +19218,16 @@
       <c r="E66" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="G66" s="39" t="s">
+      <c r="G66" s="10" t="s">
         <v>534</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="29">
         <v>39634</v>
       </c>
-      <c r="J66" s="30">
+      <c r="J66" s="29">
         <v>44805</v>
       </c>
       <c r="K66" s="5">
@@ -19234,7 +19266,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19253,178 +19285,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="71" t="s">
         <v>740</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="72" t="s">
         <v>741</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="72" t="s">
         <v>742</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="73" t="s">
         <v>743</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="69" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="69" t="s">
         <v>745</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="70" t="s">
         <v>746</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="69" t="s">
         <v>747</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="69" t="s">
         <v>748</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="69" t="s">
         <v>749</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="75" t="s">
         <v>750</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="H9" s="75" t="s">
         <v>751</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="34" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="78" t="s">
+      <c r="J9" s="70" t="s">
         <v>753</v>
       </c>
-      <c r="K9" s="79" t="s">
+      <c r="K9" s="76" t="s">
         <v>887</v>
       </c>
-      <c r="L9" s="77" t="s">
+      <c r="L9" s="75" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="37" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="34" t="s">
         <v>755</v>
       </c>
-      <c r="J10" s="78"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="77"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="75"/>
     </row>
     <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
@@ -19439,10 +19471,10 @@
       <c r="D11" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>43409</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>40700</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -19477,10 +19509,10 @@
       <c r="D12" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>43409</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <v>41640</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -19515,10 +19547,10 @@
       <c r="D13" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>43409</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>40747</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -19553,10 +19585,10 @@
       <c r="D14" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>44231</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <v>41496</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -19582,10 +19614,10 @@
       <c r="D15" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>44231</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <v>41342</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -19620,10 +19652,10 @@
       <c r="D16" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>44231</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>40179</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -19658,10 +19690,10 @@
       <c r="D17" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>44231</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <v>40952</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -19696,7 +19728,7 @@
       <c r="D18" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>44231</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -19728,10 +19760,10 @@
       <c r="D19" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>43195</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <v>41045</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -19766,10 +19798,10 @@
       <c r="D20" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>44809</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <v>40910</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -19804,10 +19836,10 @@
       <c r="D21" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>44862</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>39448</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -19842,10 +19874,10 @@
       <c r="D22" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>45150</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="28">
         <v>40974</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -19877,10 +19909,10 @@
       <c r="D23" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <v>44596</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <v>41040</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -19915,10 +19947,10 @@
       <c r="D24" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="29">
         <v>44596</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <v>41640</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -19953,10 +19985,10 @@
       <c r="D25" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <v>44231</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <v>41366</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -19988,10 +20020,10 @@
       <c r="D26" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <v>44517</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <v>41066</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -20026,10 +20058,10 @@
       <c r="D27" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <v>44809</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="28">
         <v>40887</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -20064,10 +20096,10 @@
       <c r="D28" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="29">
         <v>45150</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="29">
         <v>40946</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -20363,29 +20395,29 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:H8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20404,178 +20436,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="71" t="s">
         <v>740</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="72" t="s">
         <v>741</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="72" t="s">
         <v>742</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="73" t="s">
         <v>743</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="69" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="69" t="s">
         <v>745</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="70" t="s">
         <v>746</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="69" t="s">
         <v>747</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="69" t="s">
         <v>748</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="69" t="s">
         <v>749</v>
       </c>
-      <c r="G9" s="76" t="s">
+      <c r="G9" s="69" t="s">
         <v>750</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="H9" s="75" t="s">
         <v>751</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="34" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="78" t="s">
+      <c r="J9" s="70" t="s">
         <v>753</v>
       </c>
-      <c r="K9" s="79" t="s">
+      <c r="K9" s="76" t="s">
         <v>878</v>
       </c>
-      <c r="L9" s="77" t="s">
+      <c r="L9" s="75" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="37" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="34" t="s">
         <v>755</v>
       </c>
-      <c r="J10" s="78"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="77"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="75"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
@@ -20590,10 +20622,10 @@
       <c r="D11" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>44440</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>39583</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -20625,10 +20657,10 @@
       <c r="D12" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>44440</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <v>40636</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -20660,10 +20692,10 @@
       <c r="D13" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>44440</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <v>40257</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -20698,10 +20730,10 @@
       <c r="D14" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>44440</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <v>41702</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -20736,10 +20768,10 @@
       <c r="D15" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>44440</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <v>39083</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -20774,10 +20806,10 @@
       <c r="D16" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>44440</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>42783</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -20809,10 +20841,10 @@
       <c r="D17" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>44441</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <v>40068</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -20847,10 +20879,10 @@
       <c r="D18" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>44441</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>41859</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -20885,10 +20917,10 @@
       <c r="D19" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>44441</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <v>39083</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -20923,10 +20955,10 @@
       <c r="D20" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>44441</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <v>40940</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -20961,10 +20993,10 @@
       <c r="D21" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>44604</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>41045</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -20999,10 +21031,10 @@
       <c r="D22" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="29">
         <v>44604</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="28">
         <v>41131</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -21034,10 +21066,10 @@
       <c r="D23" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <v>44604</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <v>40341</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -21069,10 +21101,10 @@
       <c r="D24" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="29">
         <v>44604</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <v>40344</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -21107,10 +21139,10 @@
       <c r="D25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <v>44604</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <v>41408</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -21145,10 +21177,10 @@
       <c r="D26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <v>44897</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="28">
         <v>40299</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -21183,10 +21215,10 @@
       <c r="D27" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <v>44441</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="28">
         <v>40975</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -21221,10 +21253,10 @@
       <c r="D28" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="29">
         <v>44441</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="28">
         <v>40836</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -21259,10 +21291,10 @@
       <c r="D29" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>44441</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="28">
         <v>41289</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -21291,10 +21323,10 @@
       <c r="D30" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="29">
         <v>44441</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <v>42139</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -21326,10 +21358,10 @@
       <c r="D31" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="29">
         <v>44441</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="28">
         <v>42705</v>
       </c>
       <c r="G31" s="6" t="s">
@@ -21364,10 +21396,10 @@
       <c r="D32" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="29">
         <v>44441</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="28">
         <v>42370</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -21399,10 +21431,10 @@
       <c r="D33" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="29">
         <v>44441</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="28">
         <v>42263</v>
       </c>
       <c r="G33" s="6" t="s">
@@ -21434,10 +21466,10 @@
       <c r="D34" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="29">
         <v>44441</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="28">
         <v>41061</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -21472,10 +21504,10 @@
       <c r="D35" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="29">
         <v>44441</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="28">
         <v>42374</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -21507,10 +21539,10 @@
       <c r="D36" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="29">
         <v>44604</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="28">
         <v>42743</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -21545,10 +21577,10 @@
       <c r="D37" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="29">
         <v>44604</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="28">
         <v>42333</v>
       </c>
       <c r="G37" s="6" t="s">
@@ -21580,10 +21612,10 @@
       <c r="D38" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="29">
         <v>44897</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="28">
         <v>41095</v>
       </c>
       <c r="G38" s="6" t="s">
@@ -21618,10 +21650,10 @@
       <c r="D39" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="29">
         <v>44788</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="28">
         <v>42070</v>
       </c>
       <c r="G39" s="6" t="s">
@@ -21974,29 +22006,29 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:H8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22009,184 +22041,184 @@
     <col min="8" max="8" width="13.42578125" style="5" customWidth="1"/>
     <col min="9" max="9" width="15.28515625" style="5" customWidth="1"/>
     <col min="10" max="10" width="14.140625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="5" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="71" t="s">
         <v>740</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="72" t="s">
         <v>741</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="72" t="s">
         <v>742</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="73" t="s">
         <v>743</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="69" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="69" t="s">
         <v>745</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="70" t="s">
         <v>746</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="69" t="s">
         <v>747</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="69" t="s">
         <v>748</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="69" t="s">
         <v>749</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="75" t="s">
         <v>750</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="H9" s="75" t="s">
         <v>751</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="34" t="s">
         <v>752</v>
       </c>
-      <c r="J9" s="78" t="s">
+      <c r="J9" s="70" t="s">
         <v>753</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="34" t="s">
         <v>878</v>
       </c>
-      <c r="L9" s="77" t="s">
+      <c r="L9" s="75" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="37" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="34" t="s">
         <v>755</v>
       </c>
-      <c r="J10" s="78"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="77"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="75"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
@@ -22201,10 +22233,10 @@
       <c r="D11" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>43195</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>41345</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -22239,10 +22271,10 @@
       <c r="D12" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <v>43409</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>39916</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -22277,10 +22309,10 @@
       <c r="D13" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="29">
         <v>44231</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>41398</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -22315,10 +22347,10 @@
       <c r="D14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>44231</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <v>40623</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -22353,10 +22385,10 @@
       <c r="D15" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>44847</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>41080</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -22391,10 +22423,10 @@
       <c r="D16" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>43195</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <v>41807</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -22429,10 +22461,10 @@
       <c r="D17" s="5" t="s">
         <v>839</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <v>43507</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <v>40375</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -22467,10 +22499,10 @@
       <c r="D18" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>44231</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>40936</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -22505,10 +22537,10 @@
       <c r="D19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>43507</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>41640</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -22543,10 +22575,10 @@
       <c r="D20" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <v>44813</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <v>40821</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -22581,10 +22613,10 @@
       <c r="D21" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>44813</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <v>41469</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -22877,21 +22909,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="E8:H8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
